--- a/results/job_matches_2026-03-22.xlsx
+++ b/results/job_matches_2026-03-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>ANALYTICS ENGINEER-REMOTE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ESFM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a791d73f0d13a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=38159760e31a6501</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=036c0aeccda18107</t>
+          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANALYTICS ENGINEER-REMOTE</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESFM</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38159760e31a6501</t>
+          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Mojo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,172 +636,172 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b81ca9e34e5e9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1bf9814b26294f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c71629e4ae31f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7f69e6323aac3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b820a060e96568</t>
+          <t>https://www.indeed.com/viewjob?jk=301aa4b0b4fd5797</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Data Innovation and Tools Rationalization</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ce993d8d61236e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7441a0228ce5cc36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mojo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd37297befbf8cb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=bdad3b14d5aa7ef9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) / DevOps Engineer -Software Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,85 +871,1520 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6608f255a410f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e973ff60b5d8b5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DevCo Management</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d90e57e425c8b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=23541bb3e0234f95</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=540bedec5667d65d</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df643bc56ea0da7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=077982ab60e35b64</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fdd5a66207d635b</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b55acb2c23d93ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f62e9fb73e5d3de</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0e51ef1159a22dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5ad92f1774b1c8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2429dd932ad6e4eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=064f8336989796db</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ecd0341e948b071</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a65a60fb4f81e8f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47f46f151d5e738a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9347fd7bddaacff</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18110c439b8ebdac</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2273804a975fa04e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14e93d73bdb57756</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a4c2548f21f7a28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6adec3409d7b3e50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59d113c4ff0f0319</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efc4671ee3bf4278</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95da6c101f969f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cadca13573bbb5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=682d571590b6aa70</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=990159d67d30fb7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aadea691bf275ffe</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=691c875c601a48a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6e9cae5190a12fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9856e457e92e3168</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=289978ee16a63f7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f86a3d5b071c12f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c3db5a7119b5059</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9669c1c3080770b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f828df10f62125a</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7d2fb8c0fbc8112</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04f5413213fe94f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a734846d8c7f51f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbcd92f292ceec6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=059fcfa73410416c</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494bb252de8bb0cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7aef75cb3b0824f</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>Cloud Engineer</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Verinext</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Louisville, KY, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D56" t="n">
         <v>10.4</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
         </is>

--- a/results/job_matches_2026-03-22.xlsx
+++ b/results/job_matches_2026-03-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0673331b89873626</t>
+          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
         </is>
       </c>
     </row>
@@ -608,35 +608,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>Data Engineer (Remote Available)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Vanderbilt University Medical Center</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
         </is>
       </c>
     </row>
@@ -2358,35 +2358,105 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Solutions Developer for the Office of HPD TECH</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>New York City Department of Housing Preservation &amp; Development</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ab98ea9cc28ff7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Cloud Engineer</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Verinext</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Louisville, KY, US USA</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D57" t="n">
         <v>10.4</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>St. David's HealthCare</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-22.xlsx
+++ b/results/job_matches_2026-03-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SENIOR PRODUCT ENGINEER (HYBRID CHICAGO)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Mojo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db7fd563fd960a2d</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer (Remote Available)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mojo</t>
+          <t>Vanderbilt University Medical Center</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote Available)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1bf9814b26294f</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1bf9814b26294f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7f69e6323aac3</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7f69e6323aac3</t>
+          <t>https://www.indeed.com/viewjob?jk=301aa4b0b4fd5797</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301aa4b0b4fd5797</t>
+          <t>https://www.indeed.com/viewjob?jk=7441a0228ce5cc36</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7441a0228ce5cc36</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd37297befbf8cb</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd37297befbf8cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bdad3b14d5aa7ef9</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdad3b14d5aa7ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e973ff60b5d8b5</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e973ff60b5d8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=23541bb3e0234f95</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23541bb3e0234f95</t>
+          <t>https://www.indeed.com/viewjob?jk=540bedec5667d65d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=540bedec5667d65d</t>
+          <t>https://www.indeed.com/viewjob?jk=df643bc56ea0da7c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df643bc56ea0da7c</t>
+          <t>https://www.indeed.com/viewjob?jk=077982ab60e35b64</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077982ab60e35b64</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdd5a66207d635b</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdd5a66207d635b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b55acb2c23d93ff</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b55acb2c23d93ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0f62e9fb73e5d3de</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f62e9fb73e5d3de</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e51ef1159a22dc</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e51ef1159a22dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ad92f1774b1c8a</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ad92f1774b1c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=2429dd932ad6e4eb</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2429dd932ad6e4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=064f8336989796db</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064f8336989796db</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecd0341e948b071</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecd0341e948b071</t>
+          <t>https://www.indeed.com/viewjob?jk=a65a60fb4f81e8f6</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65a60fb4f81e8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=47f46f151d5e738a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47f46f151d5e738a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9347fd7bddaacff</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9347fd7bddaacff</t>
+          <t>https://www.indeed.com/viewjob?jk=18110c439b8ebdac</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18110c439b8ebdac</t>
+          <t>https://www.indeed.com/viewjob?jk=2273804a975fa04e</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2273804a975fa04e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e93d73bdb57756</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e93d73bdb57756</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4c2548f21f7a28</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4c2548f21f7a28</t>
+          <t>https://www.indeed.com/viewjob?jk=6adec3409d7b3e50</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adec3409d7b3e50</t>
+          <t>https://www.indeed.com/viewjob?jk=59d113c4ff0f0319</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d113c4ff0f0319</t>
+          <t>https://www.indeed.com/viewjob?jk=efc4671ee3bf4278</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efc4671ee3bf4278</t>
+          <t>https://www.indeed.com/viewjob?jk=95da6c101f969f95</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95da6c101f969f95</t>
+          <t>https://www.indeed.com/viewjob?jk=4cadca13573bbb5d</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cadca13573bbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=682d571590b6aa70</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682d571590b6aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=990159d67d30fb7c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990159d67d30fb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=aadea691bf275ffe</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadea691bf275ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=691c875c601a48a2</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691c875c601a48a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e9cae5190a12fc</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e9cae5190a12fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9856e457e92e3168</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9856e457e92e3168</t>
+          <t>https://www.indeed.com/viewjob?jk=289978ee16a63f7d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289978ee16a63f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a3d5b071c12f2</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a3d5b071c12f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3db5a7119b5059</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3db5a7119b5059</t>
+          <t>https://www.indeed.com/viewjob?jk=9669c1c3080770b9</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9669c1c3080770b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4f828df10f62125a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f828df10f62125a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d2fb8c0fbc8112</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d2fb8c0fbc8112</t>
+          <t>https://www.indeed.com/viewjob?jk=04f5413213fe94f2</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f5413213fe94f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a734846d8c7f51f0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a734846d8c7f51f0</t>
+          <t>https://www.indeed.com/viewjob?jk=cbcd92f292ceec6e</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbcd92f292ceec6e</t>
+          <t>https://www.indeed.com/viewjob?jk=059fcfa73410416c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059fcfa73410416c</t>
+          <t>https://www.indeed.com/viewjob?jk=494bb252de8bb0cb</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494bb252de8bb0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e7aef75cb3b0824f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,112 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7aef75cb3b0824f</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Solutions Developer for the Office of HPD TECH</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>New York City Department of Housing Preservation &amp; Development</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab98ea9cc28ff7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Verinext</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a12794620257c6fd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-22.xlsx
+++ b/results/job_matches_2026-03-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer Sr - Check Modernization and Adjustment Team</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Mojo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b695d5219c5f3d42</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer (Remote Available)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mojo</t>
+          <t>Vanderbilt University Medical Center</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote Available)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1bf9814b26294f</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1bf9814b26294f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7f69e6323aac3</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7f69e6323aac3</t>
+          <t>https://www.indeed.com/viewjob?jk=301aa4b0b4fd5797</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301aa4b0b4fd5797</t>
+          <t>https://www.indeed.com/viewjob?jk=7441a0228ce5cc36</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7441a0228ce5cc36</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd37297befbf8cb</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd37297befbf8cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bdad3b14d5aa7ef9</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdad3b14d5aa7ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e973ff60b5d8b5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e973ff60b5d8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=23541bb3e0234f95</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23541bb3e0234f95</t>
+          <t>https://www.indeed.com/viewjob?jk=540bedec5667d65d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=540bedec5667d65d</t>
+          <t>https://www.indeed.com/viewjob?jk=df643bc56ea0da7c</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df643bc56ea0da7c</t>
+          <t>https://www.indeed.com/viewjob?jk=077982ab60e35b64</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077982ab60e35b64</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdd5a66207d635b</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdd5a66207d635b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b55acb2c23d93ff</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b55acb2c23d93ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0f62e9fb73e5d3de</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f62e9fb73e5d3de</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e51ef1159a22dc</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e51ef1159a22dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ad92f1774b1c8a</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ad92f1774b1c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=2429dd932ad6e4eb</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2429dd932ad6e4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=064f8336989796db</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064f8336989796db</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecd0341e948b071</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecd0341e948b071</t>
+          <t>https://www.indeed.com/viewjob?jk=a65a60fb4f81e8f6</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65a60fb4f81e8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=47f46f151d5e738a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47f46f151d5e738a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9347fd7bddaacff</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9347fd7bddaacff</t>
+          <t>https://www.indeed.com/viewjob?jk=18110c439b8ebdac</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18110c439b8ebdac</t>
+          <t>https://www.indeed.com/viewjob?jk=2273804a975fa04e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2273804a975fa04e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e93d73bdb57756</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e93d73bdb57756</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4c2548f21f7a28</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4c2548f21f7a28</t>
+          <t>https://www.indeed.com/viewjob?jk=6adec3409d7b3e50</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adec3409d7b3e50</t>
+          <t>https://www.indeed.com/viewjob?jk=59d113c4ff0f0319</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d113c4ff0f0319</t>
+          <t>https://www.indeed.com/viewjob?jk=efc4671ee3bf4278</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efc4671ee3bf4278</t>
+          <t>https://www.indeed.com/viewjob?jk=95da6c101f969f95</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95da6c101f969f95</t>
+          <t>https://www.indeed.com/viewjob?jk=4cadca13573bbb5d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cadca13573bbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=682d571590b6aa70</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682d571590b6aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=990159d67d30fb7c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990159d67d30fb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=aadea691bf275ffe</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadea691bf275ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=691c875c601a48a2</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691c875c601a48a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e9cae5190a12fc</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e9cae5190a12fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9856e457e92e3168</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9856e457e92e3168</t>
+          <t>https://www.indeed.com/viewjob?jk=289978ee16a63f7d</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289978ee16a63f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a3d5b071c12f2</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a3d5b071c12f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3db5a7119b5059</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3db5a7119b5059</t>
+          <t>https://www.indeed.com/viewjob?jk=9669c1c3080770b9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9669c1c3080770b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4f828df10f62125a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f828df10f62125a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d2fb8c0fbc8112</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d2fb8c0fbc8112</t>
+          <t>https://www.indeed.com/viewjob?jk=04f5413213fe94f2</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f5413213fe94f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a734846d8c7f51f0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a734846d8c7f51f0</t>
+          <t>https://www.indeed.com/viewjob?jk=cbcd92f292ceec6e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbcd92f292ceec6e</t>
+          <t>https://www.indeed.com/viewjob?jk=059fcfa73410416c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059fcfa73410416c</t>
+          <t>https://www.indeed.com/viewjob?jk=494bb252de8bb0cb</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494bb252de8bb0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e7aef75cb3b0824f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Verinext</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2315,41 +2315,6 @@
         </is>
       </c>
       <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7aef75cb3b0824f</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Verinext</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
         </is>

--- a/results/job_matches_2026-03-22.xlsx
+++ b/results/job_matches_2026-03-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2285,41 +2285,6 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Verinext</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Snowflake, PostgreSQL, DynamoDB, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-03-21</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=160c7358320627f2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/job_matches_2026-03-22.xlsx
+++ b/results/job_matches_2026-03-22.xlsx
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer (Remote Available)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mojo</t>
+          <t>Vanderbilt University Medical Center</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f1d3e8504a06a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote Available)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MS Excel, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf4de38a56032d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1bf9814b26294f</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1bf9814b26294f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7f69e6323aac3</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7f69e6323aac3</t>
+          <t>https://www.indeed.com/viewjob?jk=301aa4b0b4fd5797</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301aa4b0b4fd5797</t>
+          <t>https://www.indeed.com/viewjob?jk=7441a0228ce5cc36</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7441a0228ce5cc36</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd37297befbf8cb</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd37297befbf8cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bdad3b14d5aa7ef9</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdad3b14d5aa7ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e973ff60b5d8b5</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e973ff60b5d8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=23541bb3e0234f95</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23541bb3e0234f95</t>
+          <t>https://www.indeed.com/viewjob?jk=540bedec5667d65d</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=540bedec5667d65d</t>
+          <t>https://www.indeed.com/viewjob?jk=df643bc56ea0da7c</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df643bc56ea0da7c</t>
+          <t>https://www.indeed.com/viewjob?jk=077982ab60e35b64</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077982ab60e35b64</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdd5a66207d635b</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdd5a66207d635b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b55acb2c23d93ff</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b55acb2c23d93ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0f62e9fb73e5d3de</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f62e9fb73e5d3de</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e51ef1159a22dc</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e51ef1159a22dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ad92f1774b1c8a</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ad92f1774b1c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=2429dd932ad6e4eb</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2429dd932ad6e4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=064f8336989796db</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064f8336989796db</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecd0341e948b071</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecd0341e948b071</t>
+          <t>https://www.indeed.com/viewjob?jk=a65a60fb4f81e8f6</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65a60fb4f81e8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=47f46f151d5e738a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47f46f151d5e738a</t>
+          <t>https://www.indeed.com/viewjob?jk=a9347fd7bddaacff</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9347fd7bddaacff</t>
+          <t>https://www.indeed.com/viewjob?jk=18110c439b8ebdac</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18110c439b8ebdac</t>
+          <t>https://www.indeed.com/viewjob?jk=2273804a975fa04e</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2273804a975fa04e</t>
+          <t>https://www.indeed.com/viewjob?jk=14e93d73bdb57756</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e93d73bdb57756</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4c2548f21f7a28</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4c2548f21f7a28</t>
+          <t>https://www.indeed.com/viewjob?jk=6adec3409d7b3e50</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adec3409d7b3e50</t>
+          <t>https://www.indeed.com/viewjob?jk=59d113c4ff0f0319</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d113c4ff0f0319</t>
+          <t>https://www.indeed.com/viewjob?jk=efc4671ee3bf4278</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efc4671ee3bf4278</t>
+          <t>https://www.indeed.com/viewjob?jk=95da6c101f969f95</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95da6c101f969f95</t>
+          <t>https://www.indeed.com/viewjob?jk=4cadca13573bbb5d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cadca13573bbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=682d571590b6aa70</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682d571590b6aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=990159d67d30fb7c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990159d67d30fb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=aadea691bf275ffe</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadea691bf275ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=691c875c601a48a2</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691c875c601a48a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e9cae5190a12fc</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e9cae5190a12fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9856e457e92e3168</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9856e457e92e3168</t>
+          <t>https://www.indeed.com/viewjob?jk=289978ee16a63f7d</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289978ee16a63f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a3d5b071c12f2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a3d5b071c12f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3db5a7119b5059</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3db5a7119b5059</t>
+          <t>https://www.indeed.com/viewjob?jk=9669c1c3080770b9</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9669c1c3080770b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4f828df10f62125a</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f828df10f62125a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d2fb8c0fbc8112</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d2fb8c0fbc8112</t>
+          <t>https://www.indeed.com/viewjob?jk=04f5413213fe94f2</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f5413213fe94f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a734846d8c7f51f0</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a734846d8c7f51f0</t>
+          <t>https://www.indeed.com/viewjob?jk=cbcd92f292ceec6e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbcd92f292ceec6e</t>
+          <t>https://www.indeed.com/viewjob?jk=059fcfa73410416c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059fcfa73410416c</t>
+          <t>https://www.indeed.com/viewjob?jk=494bb252de8bb0cb</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,42 +2246,42 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494bb252de8bb0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e7aef75cb3b0824f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior .NET Developer (Oracle Platform Integration)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qogen, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7aef75cb3b0824f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-22.xlsx
+++ b/results/job_matches_2026-03-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ANALYTICS ENGINEER-REMOTE</t>
+          <t>Onsite Data Engineer Miami</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESFM</t>
+          <t>IT Search Corp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Cypress, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Star Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, S3, IAM, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38159760e31a6501</t>
+          <t>https://www.indeed.com/viewjob?jk=463e08c3f11e43d4</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1bf9814b26294f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ccb008b8926e48b</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7f69e6323aac3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1bf9814b26294f</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301aa4b0b4fd5797</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7f69e6323aac3</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7441a0228ce5cc36</t>
+          <t>https://www.indeed.com/viewjob?jk=301aa4b0b4fd5797</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd37297befbf8cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7441a0228ce5cc36</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdad3b14d5aa7ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd37297befbf8cb</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4e973ff60b5d8b5</t>
+          <t>https://www.indeed.com/viewjob?jk=bdad3b14d5aa7ef9</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23541bb3e0234f95</t>
+          <t>https://www.indeed.com/viewjob?jk=f4e973ff60b5d8b5</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=540bedec5667d65d</t>
+          <t>https://www.indeed.com/viewjob?jk=23541bb3e0234f95</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df643bc56ea0da7c</t>
+          <t>https://www.indeed.com/viewjob?jk=540bedec5667d65d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077982ab60e35b64</t>
+          <t>https://www.indeed.com/viewjob?jk=df643bc56ea0da7c</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdd5a66207d635b</t>
+          <t>https://www.indeed.com/viewjob?jk=077982ab60e35b64</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b55acb2c23d93ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdd5a66207d635b</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f62e9fb73e5d3de</t>
+          <t>https://www.indeed.com/viewjob?jk=4b55acb2c23d93ff</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e51ef1159a22dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f62e9fb73e5d3de</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ad92f1774b1c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e51ef1159a22dc</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2429dd932ad6e4eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ad92f1774b1c8a</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064f8336989796db</t>
+          <t>https://www.indeed.com/viewjob?jk=2429dd932ad6e4eb</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecd0341e948b071</t>
+          <t>https://www.indeed.com/viewjob?jk=064f8336989796db</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65a60fb4f81e8f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecd0341e948b071</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47f46f151d5e738a</t>
+          <t>https://www.indeed.com/viewjob?jk=a65a60fb4f81e8f6</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9347fd7bddaacff</t>
+          <t>https://www.indeed.com/viewjob?jk=47f46f151d5e738a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18110c439b8ebdac</t>
+          <t>https://www.indeed.com/viewjob?jk=a9347fd7bddaacff</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2273804a975fa04e</t>
+          <t>https://www.indeed.com/viewjob?jk=18110c439b8ebdac</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e93d73bdb57756</t>
+          <t>https://www.indeed.com/viewjob?jk=2273804a975fa04e</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4c2548f21f7a28</t>
+          <t>https://www.indeed.com/viewjob?jk=14e93d73bdb57756</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adec3409d7b3e50</t>
+          <t>https://www.indeed.com/viewjob?jk=5a4c2548f21f7a28</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59d113c4ff0f0319</t>
+          <t>https://www.indeed.com/viewjob?jk=6adec3409d7b3e50</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efc4671ee3bf4278</t>
+          <t>https://www.indeed.com/viewjob?jk=59d113c4ff0f0319</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95da6c101f969f95</t>
+          <t>https://www.indeed.com/viewjob?jk=efc4671ee3bf4278</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cadca13573bbb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=95da6c101f969f95</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682d571590b6aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=4cadca13573bbb5d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990159d67d30fb7c</t>
+          <t>https://www.indeed.com/viewjob?jk=682d571590b6aa70</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aadea691bf275ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=990159d67d30fb7c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=691c875c601a48a2</t>
+          <t>https://www.indeed.com/viewjob?jk=aadea691bf275ffe</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e9cae5190a12fc</t>
+          <t>https://www.indeed.com/viewjob?jk=691c875c601a48a2</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9856e457e92e3168</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e9cae5190a12fc</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289978ee16a63f7d</t>
+          <t>https://www.indeed.com/viewjob?jk=9856e457e92e3168</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f86a3d5b071c12f2</t>
+          <t>https://www.indeed.com/viewjob?jk=289978ee16a63f7d</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c3db5a7119b5059</t>
+          <t>https://www.indeed.com/viewjob?jk=f86a3d5b071c12f2</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9669c1c3080770b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3db5a7119b5059</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f828df10f62125a</t>
+          <t>https://www.indeed.com/viewjob?jk=9669c1c3080770b9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d2fb8c0fbc8112</t>
+          <t>https://www.indeed.com/viewjob?jk=4f828df10f62125a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f5413213fe94f2</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d2fb8c0fbc8112</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a734846d8c7f51f0</t>
+          <t>https://www.indeed.com/viewjob?jk=04f5413213fe94f2</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbcd92f292ceec6e</t>
+          <t>https://www.indeed.com/viewjob?jk=a734846d8c7f51f0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059fcfa73410416c</t>
+          <t>https://www.indeed.com/viewjob?jk=cbcd92f292ceec6e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494bb252de8bb0cb</t>
+          <t>https://www.indeed.com/viewjob?jk=059fcfa73410416c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,40 +2246,75 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7aef75cb3b0824f</t>
+          <t>https://www.indeed.com/viewjob?jk=494bb252de8bb0cb</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7aef75cb3b0824f</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Senior .NET Developer (Oracle Platform Integration)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Qogen, LLC</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D54" t="n">
         <v>11.1</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, Kafka, Oracle, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4ed942c19be14c9a</t>
         </is>
